--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:09</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>71.53</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>59.43</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>-1.04</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>41.64</v>
+        <v>41.63</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>42.68</v>
@@ -524,7 +524,7 @@
         <v>106</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>109.17</v>
+        <v>109.16</v>
       </c>
     </row>
     <row r="5">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>12.1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>71.53</v>
+        <v>71.54</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>59.44</v>
@@ -507,7 +507,7 @@
         <v>-1.04</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>41.63</v>
+        <v>41.64</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>42.68</v>
@@ -524,7 +524,7 @@
         <v>106</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>109.16</v>
+        <v>109.17</v>
       </c>
     </row>
     <row r="5">
